--- a/reports/cloud_sizing.xlsx
+++ b/reports/cloud_sizing.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cloud Sizing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DB Selection" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-Prod SIT UAT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DR Environment" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-Prod SIT UAT" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DR Environment" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -60,7 +59,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -85,11 +84,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -124,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -159,40 +153,25 @@
     <xf numFmtId="3" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -560,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -578,14 +557,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cloud Sizing – Node Distribution  |  PNB  |  24 Mar 2026</t>
+          <t>Cloud Sizing – Node Distribution  |  HDFC  |  09 Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total Worker Nodes: 9   |   Total DB Nodes: 11   |   Confidence: High</t>
+          <t>Total Worker Nodes: 4   |   Total DB Nodes: 13   |   Confidence: High</t>
         </is>
       </c>
     </row>
@@ -660,7 +639,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
@@ -688,7 +667,7 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Increased by 1 due to high mobile users</t>
+          <t>Rule-based: 45% of 4 nodes</t>
         </is>
       </c>
     </row>
@@ -712,10 +691,10 @@
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>512</v>
@@ -732,7 +711,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Reduced by 1 due to high mobile users</t>
+          <t>Rule-based: 22% of 4 nodes, adjusted to match instance family</t>
         </is>
       </c>
     </row>
@@ -744,11 +723,11 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Worker Nodes Linux/RHEL for EFK - optional</t>
+          <t>Worker Nodes Linux/RHEL for EFK</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
@@ -756,10 +735,10 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1024</v>
@@ -776,26 +755,26 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Retained due to high compliance requirements</t>
+          <t>Rule-based: 22% of 4 nodes, adjusted to match instance family, kept due to high compliance</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PGSQL Database</t>
+          <t xml:space="preserve">  SQL Server Database</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>PGSQL Database</t>
+          <t>SQL Server Database</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Linux Nodes – Database server (Primary)</t>
+          <t>Windows Nodes – Database server (Primary)</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
@@ -834,12 +813,12 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>PGSQL Database</t>
+          <t>SQL Server Database</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Linux Nodes – Cluster (etcd+haproxy, pgbackrest)</t>
+          <t>Nodes – Cluster (Always On / AD / Witness)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -878,12 +857,12 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>PGSQL Database</t>
+          <t>SQL Server Database</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Storage: SAN (Primary DB)</t>
+          <t>Storage: SAN (Primary SQL Server DB)</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
@@ -905,7 +884,7 @@
         </is>
       </c>
       <c r="G11" s="8" t="n">
-        <v>2100</v>
+        <v>100</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
@@ -919,7 +898,7 @@
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>SAN = data_size_gb (2100 GB)</t>
+          <t>SAN = data_size_gb (100 GB)</t>
         </is>
       </c>
     </row>
@@ -960,7 +939,7 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>5900</v>
+        <v>100</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
@@ -974,26 +953,26 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>S3 = s3_size_gb (5900 GB)</t>
+          <t>S3 = s3_size_gb (100 GB)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Security &amp; Compliance</t>
+          <t xml:space="preserve">  SQL Server Database – Reporting</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Security &amp; Compliance</t>
+          <t>SQL Server Database – Reporting</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>WAF + AWS Shield Advanced</t>
+          <t>Windows Nodes – Database server (Reporting)</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -1001,23 +980,17 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Managed Service</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Memory Intensive</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>128</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>300</v>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
@@ -1026,24 +999,24 @@
       </c>
       <c r="I15" s="8" t="inlineStr">
         <is>
-          <t>AWS Managed</t>
+          <t>Self-Hosted</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>High compliance / audit – user opted in</t>
+          <t>Reporting DB server – user opted in</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Security &amp; Compliance</t>
+          <t>SQL Server Database – Reporting</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>CloudTrail + Config Audit Logs</t>
+          <t>Storage: SAN (Reporting SQL Server DB)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
@@ -1051,7 +1024,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Managed Service</t>
+          <t>10K IOPS</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1064,10 +1037,8 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G16" s="6" t="n">
+        <v>100</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
@@ -1076,31 +1047,31 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>AWS Managed</t>
+          <t>Self-Hosted</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>High compliance / audit – user opted in</t>
+          <t>Reporting SAN – user opted in</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Kubernetes Cluster</t>
+          <t xml:space="preserve">  Security &amp; Compliance</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Kubernetes Cluster</t>
+          <t>Security &amp; Compliance</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Cloud Managed K8s</t>
+          <t>WAF + AWS Shield Advanced</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
@@ -1108,467 +1079,575 @@
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
+          <t>Managed Service</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>On Demand</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>AWS Managed</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>High compliance / audit – user opted in</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Security &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>CloudTrail + Config Audit Logs</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Managed Service</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>On Demand</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>AWS Managed</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>High compliance / audit – user opted in</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Kubernetes Cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Kubernetes Cluster</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Cloud Managed K8s</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
           <t>K8s Service</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>On Demand</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>AWS Managed</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
+      <c r="J21" s="8" t="inlineStr">
         <is>
           <t>Managed control plane — always 1</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  Caching &amp; Session</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Caching &amp; Session</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Elasticache Service</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Memory Optimized</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Reserved 3 Yr</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>AWS Managed</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>Standard 2-node cache cluster</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Infrastructure &amp; Monitoring</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Infrastructure &amp; Monitoring</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Load Balancer (Internal + External)</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>ALB</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>On Demand</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>AWS Managed</t>
-        </is>
-      </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>1 internal + 1 external ALB</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>Caching &amp; Session</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Elasticache Service</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Memory Optimized</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Reserved 3 Yr</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>AWS Managed</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Standard 2-node cache cluster</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Infrastructure &amp; Monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
           <t>Infrastructure &amp; Monitoring</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Load Balancer (Internal + External)</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>On Demand</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>AWS Managed</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>1 internal + 1 external ALB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure &amp; Monitoring</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Bastion Host</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>General Purpose</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E26" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="F26" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G26" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>Reserved 3 Yr</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>AWS Managed</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>Single bastion for SSH access</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Infrastructure &amp; Monitoring</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>NAT Gateway</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C27" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>NAT</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>On Demand</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>AWS Managed</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>One per AZ for HA</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Infrastructure &amp; Monitoring</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Image Registry (ECR)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C28" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Managed Service</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="n">
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n">
         <v>512</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>On Demand</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>AWS Managed</t>
         </is>
       </c>
-      <c r="J25" s="6" t="inlineStr">
+      <c r="J28" s="6" t="inlineStr">
         <is>
           <t>Container image storage</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>Infrastructure &amp; Monitoring</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>Back Up - DB &amp; Infra Logs</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n">
+      <c r="C29" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Cloud Storage Service</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="n">
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="n">
         <v>5120</v>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>On Demand</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>AWS Managed</t>
         </is>
       </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>As per bank backup policy</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Sizing Inputs (from Sizing Template)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Total Worker Nodes</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr"/>
-      <c r="D29" s="6" t="inlineStr"/>
-      <c r="E29" s="6" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr"/>
-      <c r="G29" s="6" t="inlineStr"/>
-      <c r="H29" s="6" t="inlineStr"/>
-      <c r="I29" s="6" t="inlineStr"/>
-      <c r="J29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="B32" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr"/>
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr"/>
+      <c r="I32" s="6" t="inlineStr"/>
+      <c r="J32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>Total vCPUs (Worker)</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B33" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="C33" s="8" t="inlineStr"/>
+      <c r="D33" s="8" t="inlineStr"/>
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr"/>
+      <c r="J33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Total RAM GB (Worker)</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>88</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr"/>
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="6" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr"/>
+      <c r="I34" s="6" t="inlineStr"/>
+      <c r="J34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>SQL Server RAM GB</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
         <v>96</v>
       </c>
-      <c r="C30" s="8" t="inlineStr"/>
-      <c r="D30" s="8" t="inlineStr"/>
-      <c r="E30" s="8" t="inlineStr"/>
-      <c r="F30" s="8" t="inlineStr"/>
-      <c r="G30" s="8" t="inlineStr"/>
-      <c r="H30" s="8" t="inlineStr"/>
-      <c r="I30" s="8" t="inlineStr"/>
-      <c r="J30" s="8" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Total RAM GB (Worker)</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>172</v>
-      </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>PostgreSQL RAM GB</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n">
-        <v>224</v>
-      </c>
-      <c r="C32" s="8" t="inlineStr"/>
-      <c r="D32" s="8" t="inlineStr"/>
-      <c r="E32" s="8" t="inlineStr"/>
-      <c r="F32" s="8" t="inlineStr"/>
-      <c r="G32" s="8" t="inlineStr"/>
-      <c r="H32" s="8" t="inlineStr"/>
-      <c r="I32" s="8" t="inlineStr"/>
-      <c r="J32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr"/>
+      <c r="D35" s="8" t="inlineStr"/>
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr"/>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr"/>
+      <c r="J35" s="8" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Data Size GB</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n">
-        <v>2100</v>
-      </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="B36" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr"/>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
+      <c r="F36" s="6" t="inlineStr"/>
+      <c r="G36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr"/>
+      <c r="J36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>S3 Size GB</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n">
-        <v>5900</v>
-      </c>
-      <c r="C34" s="8" t="inlineStr"/>
-      <c r="D34" s="8" t="inlineStr"/>
-      <c r="E34" s="8" t="inlineStr"/>
-      <c r="F34" s="8" t="inlineStr"/>
-      <c r="G34" s="8" t="inlineStr"/>
-      <c r="H34" s="8" t="inlineStr"/>
-      <c r="I34" s="8" t="inlineStr"/>
-      <c r="J34" s="8" t="inlineStr"/>
+      <c r="B37" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C37" s="8" t="inlineStr"/>
+      <c r="D37" s="8" t="inlineStr"/>
+      <c r="E37" s="8" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
+      <c r="J37" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A22:J22"/>
     <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A21:J21"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A24:J24"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A19:J19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1580,225 +1659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Database Selection &amp; Hosting Model  |  PNB</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Database</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Hosting Model</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>AWS Service</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Estimated Monthly (USD)</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>PostgreSQL</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>Relational / Open Source</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>Self-Hosted on EC2</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>EC2 r5.8xlarge × 2 + EBS io2</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>2943.36</v>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>PostgreSQL is open-source; self-hosted on EC2 avoids RDS licensing premium. HA via Patroni + etcd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>SQL Server</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>Relational / Commercial</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>AWS Managed (RDS)</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>RDS for SQL Server Multi-AZ</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>11648</v>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>SQL Server requires Microsoft licensing; RDS Managed handles patching, backups, and HA automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>Relational / Commercial</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>AWS Managed (RDS)</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>RDS for Oracle Multi-AZ</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>9856</v>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>Oracle licensing is complex; RDS Oracle reduces compliance risk and operational overhead.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>ElastiCache (Redis)</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>In-Memory / Cache</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>AWS Managed</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>ElastiCache r6g.large × 2</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>481.8</v>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>Session store and API cache; always managed — no viable self-hosted alternative on AWS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Self-Hosted on EC2 — lower cost, more control, requires DBA expertise</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>AWS Managed (RDS) — higher cost, zero ops overhead, commercial license compliance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B10:F10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1814,14 +1675,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Pre-Prod / SIT / UAT Environment  |  PNB  |  DB: PostgreSQL</t>
+          <t>Pre-Prod / SIT / UAT Environment  |  HDFC  |  DB: SQL Server</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Monthly: $10,147.47   |   Annual: $121,769.64</t>
+          <t>Monthly: $3,397.85   |   Annual: $40,774.20</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1764,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="12" t="n">
         <v>73</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -1937,7 +1798,7 @@
       <c r="F6" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="13" t="n">
         <v>1169.28</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -1971,7 +1832,7 @@
       <c r="F7" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="12" t="n">
         <v>321.28</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -2005,7 +1866,7 @@
       <c r="F8" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="13" t="n">
         <v>601.6</v>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -2017,19 +1878,19 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PGSQL DB</t>
+          <t xml:space="preserve">  S3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>PGSQL DB</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>DB Server (Pre-Prod)</t>
+          <t>S3 Storage + Replication</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
@@ -2037,199 +1898,195 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>m5.4xlarge</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>584.64</v>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>34.5</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>1× m5.4xlarge @ $0.7680/hr + 300GB EBS</t>
+          <t>1500GB S3</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>PGSQL DB</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Storage: SAN Pre-Prod</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Caching</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Caching</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Caching Service (ElastiCache)</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>EBS io2</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>125</v>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>1× 1000GB io2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>PGSQL DB</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Storage: SAN SIT</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>cache.r6g.large</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>121.18</v>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>1× ElastiCache</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Load Balancer (Internal + External)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>EBS io2</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>1× 500GB io2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>PGSQL DB</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Storage: SAN UAT</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>1× ALB</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>NAT Gateway</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>NAT</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>2× NAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Bastion Host</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>EBS io2</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>1× 500GB io2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>S3 Storage + Replication</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>1500GB S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Caching</t>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>m5.large</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>94.08</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>1× m5.large @ $0.0960/hr + 300GB EBS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Caching</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Caching Service (ElastiCache)</t>
+          <t>Image Registry (ECR)</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
@@ -2237,40 +2094,44 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>cache.r6g.large</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>121.18</v>
+          <t>ECR</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>50</v>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>1× ElastiCache</t>
+          <t>500GB ECR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Infrastructure</t>
+          <t xml:space="preserve">  Backup</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Backup</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Load Balancer (Internal + External)</t>
+          <t>Back Up – DB &amp; Infra Logs</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
@@ -2278,7 +2139,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -2291,208 +2152,100 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="18" t="n">
-        <v>16.43</v>
+      <c r="G19" s="12" t="n">
+        <v>34.5</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>1× ALB</t>
+          <t>1500GB S3</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>NAT Gateway</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>2× NAT</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PGSQL DB</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Bastion Host</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>m5.large</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G21" s="18" t="n">
-        <v>94.08</v>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>1× m5.large @ $0.0960/hr + 300GB EBS</t>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>PGSQL DB</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>db.r5.2xlarge</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>850</v>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>RDS SQL Server db.r5.2xlarge Single-AZ (Pre-Prod)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Image Registry (ECR)</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>ECR</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="n">
-        <v>50</v>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>500GB ECR</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Backup</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Backup</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Back Up – DB &amp; Infra Logs</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="18" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>1500GB S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr"/>
-      <c r="C25" s="17" t="inlineStr"/>
-      <c r="D25" s="17" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr"/>
-      <c r="F25" s="17" t="inlineStr"/>
-      <c r="G25" s="21" t="n">
-        <v>10147.47</v>
-      </c>
-      <c r="H25" s="17" t="inlineStr"/>
+      <c r="B22" s="14" t="inlineStr"/>
+      <c r="C22" s="15" t="inlineStr"/>
+      <c r="D22" s="15" t="inlineStr"/>
+      <c r="E22" s="15" t="inlineStr"/>
+      <c r="F22" s="15" t="inlineStr"/>
+      <c r="G22" s="16" t="n">
+        <v>3397.85</v>
+      </c>
+      <c r="H22" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A20:H20"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A11:H11"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A23:H23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2509,19 +2262,19 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Disaster Recovery Environment  |  PNB  |  DB: PostgreSQL  |  Inflation: 4%/yr</t>
+          <t>Disaster Recovery Environment  |  HDFC  |  DB: SQL Server  |  Inflation: 4%/yr</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Monthly: $9,391.94   |   Annual: $112,703.28   |   5-Year Total: $634,854.81</t>
+          <t>Monthly: $7,718.78   |   Annual: $92,625.36   |   5-Year Total: $521,756.37</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  5-Year DR Cost Forecast (4% inflation/year)</t>
         </is>
@@ -2571,42 +2324,42 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Annual DR Cost</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
-        <v>117211.41</v>
-      </c>
-      <c r="C5" s="21" t="n">
-        <v>121899.87</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>126775.86</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>131846.9</v>
-      </c>
-      <c r="F5" s="21" t="n">
-        <v>137120.77</v>
-      </c>
-      <c r="G5" s="21" t="n">
-        <v>634854.8100000001</v>
-      </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="B5" s="18" t="n">
+        <v>96330.37</v>
+      </c>
+      <c r="C5" s="16" t="n">
+        <v>100183.59</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>104190.93</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>108358.57</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>112692.91</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>521756.37</v>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>1.0400×</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>1.2167×</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  Role-by-Role Breakdown</t>
         </is>
@@ -2691,7 +2444,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="G10" s="12" t="n">
         <v>73</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -2726,7 +2479,7 @@
       <c r="F11" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="13" t="n">
         <v>2324.48</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -2761,7 +2514,7 @@
       <c r="F12" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="12" t="n">
         <v>642.5599999999999</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -2796,7 +2549,7 @@
       <c r="F13" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="G13" s="19" t="n">
+      <c r="G13" s="13" t="n">
         <v>724.48</v>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -2809,515 +2562,373 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  PGSQL DB</t>
+          <t xml:space="preserve">  S3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>PGSQL DB</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>DB Server Primary – DR</t>
+          <t>S3 Storage + Replication – DR</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>184</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>8000GB S3</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Caching</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Caching</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Elasticache Service – DR</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>m5.8xlarge</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>128</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>2290.56</v>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>2× m5.8xlarge @ $1.5360/hr + 300GB EBS</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>PGSQL DB</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>DB Cluster (etcd+haproxy) – DR</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>cache.r6g.large</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>m5.large</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>312.32</v>
-      </c>
-      <c r="H16" s="8" t="inlineStr">
-        <is>
-          <t>4× m5.large @ $0.0960/hr + 100GB EBS</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>PGSQL DB</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Storage: SAN Primary – DR</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>EBS io2</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="n">
-        <v>750</v>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>2× 3000GB io2</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr"/>
+      <c r="F17" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>242.36</v>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>2× ElastiCache</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>PGSQL DB</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Reporting DB – DR</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>m5.8xlarge</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>128</v>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>1145.28</v>
-      </c>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>1× m5.8xlarge @ $1.5360/hr + 300GB EBS</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Infrastructure</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>PGSQL DB</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Storage: SAN Reporting – DR</t>
+          <t>Load Balancer – DR</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>2× ALB</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>NAT Gateway – DR</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>NAT</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>2× NAT</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Bastion Host – DR</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>EBS io2</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="n">
-        <v>375</v>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>1× 3000GB io2</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>m5.large</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>94.08</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>1× m5.large @ $0.0960/hr + 300GB EBS</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Image Registry (ECR) – DR</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>ECR</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>512GB ECR</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Backup</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Backup</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Back Up – DR</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>S3</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>S3 Storage + Replication – DR</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="19" t="n">
-        <v>184</v>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>8000GB S3</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Caching</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Caching</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Elasticache Service – DR</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>cache.r6g.large</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="G23" s="18" t="n">
-        <v>242.36</v>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>2× ElastiCache</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Infrastructure</t>
-        </is>
-      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>117.76</v>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>5120GB S3</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Load Balancer – DR</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>ALB</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="19" t="n">
-        <v>32.86</v>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>2× ALB</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="inlineStr"/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Managed DB</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>NAT Gateway – DR</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>NAT</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="n">
-        <v>32</v>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>2× NAT</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr"/>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Managed DB</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>db.r5.4xlarge</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>3200</v>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>RDS SQL Server db.r5.4xlarge Multi-AZ DR</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Bastion Host – DR</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>m5.large</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G27" s="19" t="n">
-        <v>94.08</v>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>1× m5.large @ $0.0960/hr + 300GB EBS</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Image Registry (ECR) – DR</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>ECR</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>512GB ECR</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Backup</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Backup</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Back Up – DR</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" s="19" t="n">
-        <v>117.76</v>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>5120GB S3</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr"/>
-      <c r="C31" s="17" t="inlineStr"/>
-      <c r="D31" s="17" t="inlineStr"/>
-      <c r="E31" s="17" t="inlineStr"/>
-      <c r="F31" s="17" t="inlineStr"/>
-      <c r="G31" s="21" t="n">
-        <v>9391.940000000001</v>
-      </c>
-      <c r="H31" s="17" t="inlineStr"/>
-      <c r="I31" s="17" t="inlineStr"/>
+      <c r="B27" s="14" t="inlineStr"/>
+      <c r="C27" s="15" t="inlineStr"/>
+      <c r="D27" s="15" t="inlineStr"/>
+      <c r="E27" s="15" t="inlineStr"/>
+      <c r="F27" s="15" t="inlineStr"/>
+      <c r="G27" s="16" t="n">
+        <v>7718.78</v>
+      </c>
+      <c r="H27" s="15" t="inlineStr"/>
+      <c r="I27" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A29:I29"/>
     <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A14:I14"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A18:I18"/>
     <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/cloud_sizing.xlsx
+++ b/reports/cloud_sizing.xlsx
@@ -578,7 +578,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cloud Sizing – Node Distribution  |  Apple FCU  |  16 Apr 2026</t>
+          <t>Cloud Sizing – Node Distribution  |  RHB  |  20 Apr 2026</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="E6" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="8" t="n">
         <v>16</v>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>32</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>512</v>
@@ -732,7 +732,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Reduced by 1 due to high mobile users, but kept due to high compliance</t>
+          <t>Retained due to high compliance requirement</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Kept due to high compliance</t>
+          <t>Retained due to high compliance requirement, adjusted to match instance family</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Database Selection &amp; Hosting Model  |  Apple FCU</t>
+          <t>Database Selection &amp; Hosting Model  |  RHB</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="E3" s="13" t="n">
-        <v>2943.36</v>
+        <v>3237.7</v>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
@@ -1814,14 +1814,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Pre-Prod / SIT / UAT Environment  |  Apple FCU  |  DB: PostgreSQL</t>
+          <t>Pre-Prod / SIT / UAT Environment  |  RHB  |  DB: PostgreSQL</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Monthly: $13,262.04   |   Annual: $159,144.48</t>
+          <t>Monthly: $13,426.83   |   Annual: $161,121.96</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>m5.4xlarge</t>
+          <t>c6i.4xlarge</t>
         </is>
       </c>
       <c r="E6" s="8" t="n">
@@ -1938,11 +1938,11 @@
         <v>19</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>2338.56</v>
+        <v>2051.49</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>4× m5.4xlarge @ $0.7680/hr + 300GB EBS</t>
+          <t>4× c6i.4xlarge @ $0.6664/hr + 300GB EBS</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>m5.2xlarge</t>
+          <t>c6i.2xlarge</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
@@ -1972,11 +1972,11 @@
         <v>16</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>321.28</v>
+        <v>288.29</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>1× m5.2xlarge @ $0.3840/hr + 512GB EBS</t>
+          <t>1× c6i.2xlarge @ $0.3332/hr + 512GB EBS</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>m5.8xlarge</t>
+          <t>c6i.12xlarge</t>
         </is>
       </c>
       <c r="E9" s="8" t="n">
@@ -2013,11 +2013,11 @@
         <v>96</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>1145.28</v>
+        <v>1485.82</v>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>1× m5.8xlarge @ $1.5360/hr + 300GB EBS</t>
+          <t>1× c6i.12xlarge @ $1.9992/hr + 300GB EBS</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="G10" s="18" t="n">
-        <v>105</v>
+        <v>115.5</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         <v>16</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>121.18</v>
+        <v>133.3</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>4</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>54.37</v>
+        <v>61.08</v>
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="G19" s="18" t="n">
-        <v>51.2</v>
+        <v>56.32</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
       <c r="E24" s="17" t="inlineStr"/>
       <c r="F24" s="17" t="inlineStr"/>
       <c r="G24" s="21" t="n">
-        <v>13262.04</v>
+        <v>13426.83</v>
       </c>
       <c r="H24" s="17" t="inlineStr"/>
     </row>
@@ -2445,14 +2445,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Disaster Recovery Environment  |  Apple FCU  |  DB: PostgreSQL  |  Inflation: 4%/yr</t>
+          <t>Disaster Recovery Environment  |  RHB  |  DB: PostgreSQL  |  Inflation: 4%/yr</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Monthly: $8,585.73   |   Annual: $103,028.76   |   5-Year Total: $580,358.48</t>
+          <t>Monthly: $10,531.08   |   Annual: $126,372.96   |   5-Year Total: $711,855.78</t>
         </is>
       </c>
     </row>
@@ -2513,22 +2513,22 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>107149.91</v>
+        <v>131427.88</v>
       </c>
       <c r="C5" s="21" t="n">
-        <v>111435.91</v>
+        <v>136684.99</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>115893.34</v>
+        <v>142152.39</v>
       </c>
       <c r="E5" s="21" t="n">
-        <v>120529.08</v>
+        <v>147838.49</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>125350.24</v>
+        <v>153752.03</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>580358.48</v>
+        <v>711855.78</v>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
@@ -2663,11 +2663,11 @@
         <v>19</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>3486.72</v>
+        <v>4343.65</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>6× m5.4xlarge @ $0.7680/hr + 256GB EBS</t>
+          <t>6× m5.4xlarge @ $0.9600/hr + 256GB EBS</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr"/>
@@ -2698,11 +2698,11 @@
         <v>16</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>642.5599999999999</v>
+        <v>793.37</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>2× m5.2xlarge @ $0.3840/hr + 512GB EBS</t>
+          <t>2× m5.2xlarge @ $0.4800/hr + 512GB EBS</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr"/>
@@ -2740,11 +2740,11 @@
         <v>136</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>3411.84</v>
+        <v>4259.04</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>2× m5.12xlarge @ $2.3040/hr + 300GB EBS</t>
+          <t>2× m5.12xlarge @ $2.8800/hr + 300GB EBS</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr"/>
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="G15" s="18" t="n">
-        <v>315</v>
+        <v>355.95</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>16</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>242.36</v>
+        <v>273.87</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>4</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>54.37</v>
+        <v>65.66</v>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="G24" s="18" t="n">
-        <v>51.2</v>
+        <v>57.86</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
       <c r="E29" s="17" t="inlineStr"/>
       <c r="F29" s="17" t="inlineStr"/>
       <c r="G29" s="21" t="n">
-        <v>8585.73</v>
+        <v>10531.08</v>
       </c>
       <c r="H29" s="17" t="inlineStr"/>
       <c r="I29" s="17" t="inlineStr"/>
